--- a/data/sample/score13-23-SK.xlsx
+++ b/data/sample/score13-23-SK.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Seo-young Silvia Kim\Documents\K-petition\data\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A744EB6A-A933-430D-BD8D-BAB48A8B775D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF3C317A-593B-411B-B516-5DD646E8B26E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3340" yWindow="3340" windowWidth="19200" windowHeight="11260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -941,11 +941,11 @@
         <v>10</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J2">
         <f>AVERAGE(E2:I2)</f>
-        <v>9.4</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="K2">
         <v>9</v>
@@ -1118,11 +1118,11 @@
         <v>10</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="K7">
         <v>10</v>
@@ -1226,11 +1226,11 @@
         <v>8</v>
       </c>
       <c r="I10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J10">
         <f t="shared" si="0"/>
-        <v>9.4</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="K10">
         <v>8</v>
@@ -1475,11 +1475,11 @@
         <v>5</v>
       </c>
       <c r="I17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J17">
         <f t="shared" si="0"/>
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="K17">
         <v>6</v>
